--- a/trust/ValueSet-Participants.xlsx
+++ b/trust/ValueSet-Participants.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="69">
   <si>
     <t>Property</t>
   </si>
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.7.2</t>
+    <t>1.7.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T12:39:37+00:00</t>
+    <t>2026-10-02T10:11:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -158,6 +158,9 @@
   </si>
   <si>
     <t>IDN</t>
+  </si>
+  <si>
+    <t>IRL</t>
   </si>
   <si>
     <t>LVA</t>
@@ -521,7 +524,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B36"/>
+  <dimension ref="A1:B37"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -736,18 +739,24 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="B35" t="s" s="2">
-        <v>30</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="B35" s="2"/>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
         <v>31</v>
       </c>
-      <c r="B36" t="s" s="2">
-        <v>67</v>
+      <c r="B37" t="s" s="2">
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/trust/ValueSet-Participants.xlsx
+++ b/trust/ValueSet-Participants.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.7.3</t>
+    <t>1.7.4</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-02T10:11:10+00:00</t>
+    <t>2026-10-12T03:23:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
